--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486909_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486909_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.1138</v>
+        <v>7.6417</v>
       </c>
       <c r="E2" t="n">
-        <v>4.7501</v>
+        <v>5.1298</v>
       </c>
       <c r="F2" t="n">
-        <v>2.3637</v>
+        <v>2.5119</v>
       </c>
       <c r="G2" t="n">
         <v>8.7003</v>
@@ -610,13 +610,13 @@
         <v>2.4641</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.5517</v>
+        <v>-1.0238</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.054</v>
+        <v>-0.6743</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.4977</v>
+        <v>-0.3495</v>
       </c>
       <c r="V2" t="n">
         <v>-0.2402</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D. BAH</t>
+          <t>O. RUSSELL</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>7.0856</v>
+        <v>5.8249</v>
       </c>
       <c r="E3" t="n">
-        <v>6.3083</v>
+        <v>4.3066</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7773</v>
+        <v>1.5183</v>
       </c>
       <c r="G3" t="n">
-        <v>2.9832</v>
+        <v>1.2331</v>
       </c>
       <c r="H3" t="n">
-        <v>1.8199</v>
+        <v>1.5017</v>
       </c>
       <c r="I3" t="n">
-        <v>1.1633</v>
+        <v>-0.2686</v>
       </c>
       <c r="J3" t="n">
-        <v>2.4347</v>
+        <v>2.1083</v>
       </c>
       <c r="K3" t="n">
-        <v>1.6454</v>
+        <v>1.6351</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7893</v>
+        <v>0.4732</v>
       </c>
       <c r="M3" t="n">
-        <v>0.5485</v>
+        <v>-0.8753</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1746</v>
+        <v>-0.1335</v>
       </c>
       <c r="O3" t="n">
-        <v>0.374</v>
+        <v>-0.7418</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.8214</v>
+        <v>2.0534</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.2588</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.4374</v>
+        <v>2.0534</v>
       </c>
       <c r="S3" t="n">
-        <v>1.3879</v>
+        <v>0.1811</v>
       </c>
       <c r="T3" t="n">
-        <v>1.1776</v>
+        <v>-0.159</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2103</v>
+        <v>0.3401</v>
       </c>
       <c r="V3" t="n">
-        <v>3.5359</v>
+        <v>2.3573</v>
       </c>
       <c r="W3" t="n">
-        <v>4.9548</v>
+        <v>2.3573</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.4189</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>O. RUSSELL</t>
+          <t>D. BAH</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.7953</v>
+        <v>5.6978</v>
       </c>
       <c r="E4" t="n">
-        <v>4.3066</v>
+        <v>5.1576</v>
       </c>
       <c r="F4" t="n">
-        <v>1.4886</v>
+        <v>0.5402</v>
       </c>
       <c r="G4" t="n">
-        <v>1.2331</v>
+        <v>2.9832</v>
       </c>
       <c r="H4" t="n">
-        <v>1.5017</v>
+        <v>1.8199</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2686</v>
+        <v>1.1633</v>
       </c>
       <c r="J4" t="n">
-        <v>2.1083</v>
+        <v>2.4347</v>
       </c>
       <c r="K4" t="n">
-        <v>1.6351</v>
+        <v>1.6454</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4732</v>
+        <v>0.7893</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.8753</v>
+        <v>0.5485</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.1335</v>
+        <v>0.1746</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.7418</v>
+        <v>0.374</v>
       </c>
       <c r="P4" t="n">
-        <v>2.0534</v>
+        <v>-0.8214</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-2.2588</v>
       </c>
       <c r="R4" t="n">
-        <v>2.0534</v>
+        <v>1.4374</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1515</v>
+        <v>0.0001</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.159</v>
+        <v>0.0269</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3105</v>
+        <v>-0.0268</v>
       </c>
       <c r="V4" t="n">
-        <v>2.3573</v>
+        <v>3.5359</v>
       </c>
       <c r="W4" t="n">
-        <v>2.3573</v>
+        <v>4.9548</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-1.4189</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.8692</v>
+        <v>4.4128</v>
       </c>
       <c r="E5" t="n">
-        <v>1.954</v>
+        <v>2.4383</v>
       </c>
       <c r="F5" t="n">
-        <v>1.9152</v>
+        <v>1.9745</v>
       </c>
       <c r="G5" t="n">
         <v>4.4805</v>
@@ -844,13 +844,13 @@
         <v>1.8481</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.7736</v>
+        <v>-1.23</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.2438</v>
+        <v>-0.7596000000000001</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.5298</v>
+        <v>-0.4705</v>
       </c>
       <c r="V5" t="n">
         <v>-0.4805</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.8441</v>
+        <v>2.2329</v>
       </c>
       <c r="E6" t="n">
-        <v>1.9452</v>
+        <v>2.3636</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.101</v>
+        <v>-0.1307</v>
       </c>
       <c r="G6" t="n">
         <v>-0.0785</v>
@@ -922,13 +922,13 @@
         <v>1.0267</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.872</v>
+        <v>-0.4833</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.651</v>
+        <v>-0.2326</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.221</v>
+        <v>-0.2507</v>
       </c>
       <c r="V6" t="n">
         <v>1.7679</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. TAMAYO LESMES</t>
+          <t>K. NEWTON</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.5237</v>
+        <v>1.9982</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7862</v>
+        <v>2.6365</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7375</v>
+        <v>-0.6383</v>
       </c>
       <c r="G7" t="n">
-        <v>1.115</v>
+        <v>3.4321</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4479</v>
+        <v>1.7906</v>
       </c>
       <c r="I7" t="n">
-        <v>1.5629</v>
+        <v>1.6415</v>
       </c>
       <c r="J7" t="n">
-        <v>2.1037</v>
+        <v>2.8261</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0779</v>
+        <v>1.8137</v>
       </c>
       <c r="L7" t="n">
-        <v>2.0258</v>
+        <v>1.0123</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.9887</v>
+        <v>0.6061</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.5258</v>
+        <v>-0.0231</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.4629</v>
+        <v>0.6291</v>
       </c>
       <c r="P7" t="n">
-        <v>1.0267</v>
+        <v>1.2321</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.0267</v>
+        <v>-0.2053</v>
       </c>
       <c r="R7" t="n">
-        <v>2.0534</v>
+        <v>1.4374</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3777</v>
+        <v>-1.5962</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2907</v>
+        <v>-0.5735</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.08699999999999999</v>
+        <v>-1.0227</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.2402</v>
+        <v>-1.0698</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.5893</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.2402</v>
+        <v>-1.6591</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>K. NEWTON</t>
+          <t>A. TAMAYO LESMES</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.486</v>
+        <v>1.1663</v>
       </c>
       <c r="E8" t="n">
-        <v>2.3614</v>
+        <v>0.577</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.8754</v>
+        <v>0.5893</v>
       </c>
       <c r="G8" t="n">
-        <v>3.4321</v>
+        <v>1.115</v>
       </c>
       <c r="H8" t="n">
-        <v>1.7906</v>
+        <v>-0.4479</v>
       </c>
       <c r="I8" t="n">
-        <v>1.6415</v>
+        <v>1.5629</v>
       </c>
       <c r="J8" t="n">
-        <v>2.8261</v>
+        <v>2.1037</v>
       </c>
       <c r="K8" t="n">
-        <v>1.8137</v>
+        <v>0.0779</v>
       </c>
       <c r="L8" t="n">
-        <v>1.0123</v>
+        <v>2.0258</v>
       </c>
       <c r="M8" t="n">
-        <v>0.6061</v>
+        <v>-0.9887</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.0231</v>
+        <v>-0.5258</v>
       </c>
       <c r="O8" t="n">
-        <v>0.6291</v>
+        <v>-0.4629</v>
       </c>
       <c r="P8" t="n">
-        <v>1.2321</v>
+        <v>1.0267</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.2053</v>
+        <v>-1.0267</v>
       </c>
       <c r="R8" t="n">
-        <v>1.4374</v>
+        <v>2.0534</v>
       </c>
       <c r="S8" t="n">
-        <v>-2.1084</v>
+        <v>-0.7352</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.8486</v>
+        <v>-0.4999</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.2598</v>
+        <v>-0.2352</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.0698</v>
+        <v>-0.2402</v>
       </c>
       <c r="W8" t="n">
-        <v>0.5893</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.6591</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>P. GARCIA CARRERO</t>
+          <t>V. RODRIGUEZ GIL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.1381</v>
+        <v>-0.5796</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.9408</v>
+        <v>-0.3461</v>
       </c>
       <c r="F9" t="n">
-        <v>1.8027</v>
+        <v>-0.2335</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.008399999999999999</v>
+        <v>0.2251</v>
       </c>
       <c r="H9" t="n">
-        <v>1.4886</v>
+        <v>-0.409</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.497</v>
+        <v>0.6341</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.1623</v>
+        <v>0.8666</v>
       </c>
       <c r="K9" t="n">
-        <v>1.0351</v>
+        <v>0.1168</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.1974</v>
+        <v>0.7498</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1539</v>
+        <v>-0.6415</v>
       </c>
       <c r="N9" t="n">
-        <v>0.4535</v>
+        <v>-0.5258</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.2996</v>
+        <v>-0.1157</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.4107</v>
+        <v>0.4107</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.2588</v>
+        <v>-1.0267</v>
       </c>
       <c r="R9" t="n">
-        <v>1.8481</v>
+        <v>1.4374</v>
       </c>
       <c r="S9" t="n">
-        <v>0.281</v>
+        <v>-0.0368</v>
       </c>
       <c r="T9" t="n">
-        <v>0.4802</v>
+        <v>-0.186</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1993</v>
+        <v>0.1492</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-1.1786</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>V. RODRIGUEZ GIL</t>
+          <t>P. GARCIA CARRERO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.8481</v>
+        <v>-0.7435</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.5553</v>
+        <v>-2.398</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2928</v>
+        <v>1.6545</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2251</v>
+        <v>-0.008399999999999999</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.409</v>
+        <v>1.4886</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6341</v>
+        <v>-1.497</v>
       </c>
       <c r="J10" t="n">
-        <v>0.8666</v>
+        <v>-0.1623</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1168</v>
+        <v>1.0351</v>
       </c>
       <c r="L10" t="n">
-        <v>0.7498</v>
+        <v>-1.1974</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.6415</v>
+        <v>0.1539</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.5258</v>
+        <v>0.4535</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.1157</v>
+        <v>-0.2996</v>
       </c>
       <c r="P10" t="n">
-        <v>0.4107</v>
+        <v>-0.4107</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.0267</v>
+        <v>-2.2588</v>
       </c>
       <c r="R10" t="n">
-        <v>1.4374</v>
+        <v>1.8481</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3053</v>
+        <v>-0.3244</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3952</v>
+        <v>0.0231</v>
       </c>
       <c r="U10" t="n">
-        <v>0.08989999999999999</v>
+        <v>-0.3475</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.1786</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.1786</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.0863</v>
+        <v>-3.677</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.4813</v>
+        <v>-2.1016</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.605</v>
+        <v>-1.5754</v>
       </c>
       <c r="G11" t="n">
         <v>-1.9933</v>
@@ -1312,13 +1312,13 @@
         <v>1.8481</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.1464</v>
+        <v>-0.7371</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6587</v>
+        <v>-0.279</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4877</v>
+        <v>-0.4581</v>
       </c>
       <c r="V11" t="n">
         <v>-1.7679</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>23.6452</v>
+        <v>23.9745</v>
       </c>
       <c r="E12" t="n">
-        <v>17.4344</v>
+        <v>17.7637</v>
       </c>
       <c r="F12" t="n">
         <v>6.210800000000001</v>
@@ -1366,7 +1366,7 @@
         <v>21.4352</v>
       </c>
       <c r="K12" t="n">
-        <v>7.756299999999999</v>
+        <v>7.7563</v>
       </c>
       <c r="L12" t="n">
         <v>13.6789</v>
@@ -1378,10 +1378,10 @@
         <v>-0.7829000000000002</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.5632</v>
+        <v>-0.5632000000000003</v>
       </c>
       <c r="P12" t="n">
-        <v>7.1869</v>
+        <v>7.186899999999999</v>
       </c>
       <c r="Q12" t="n">
         <v>-10.2671</v>
@@ -1390,13 +1390,13 @@
         <v>17.4541</v>
       </c>
       <c r="S12" t="n">
-        <v>-6.314699999999999</v>
+        <v>-5.985599999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>-3.6432</v>
+        <v>-3.3139</v>
       </c>
       <c r="U12" t="n">
-        <v>-2.6716</v>
+        <v>-2.6717</v>
       </c>
       <c r="V12" t="n">
         <v>2.6839</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.8766</v>
+        <v>2.4641</v>
       </c>
       <c r="E13" t="n">
-        <v>3.188</v>
+        <v>3.6064</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.3114</v>
+        <v>-1.1423</v>
       </c>
       <c r="G13" t="n">
         <v>0.2718</v>
@@ -1468,13 +1468,13 @@
         <v>0.8214</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.0461</v>
+        <v>0.5414</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.283</v>
+        <v>0.1354</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2369</v>
+        <v>0.406</v>
       </c>
       <c r="V13" t="n">
         <v>0.8295</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. BADMUS</t>
+          <t>G. RODRIGUEZ SOLER</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.6739000000000001</v>
+        <v>0.3658</v>
       </c>
       <c r="E14" t="n">
-        <v>0.912</v>
+        <v>0.6776</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.586</v>
+        <v>-0.3118</v>
       </c>
       <c r="G14" t="n">
-        <v>-3.433</v>
+        <v>-0.7166</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.7547</v>
+        <v>-1.7611</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.6783</v>
+        <v>1.0445</v>
       </c>
       <c r="J14" t="n">
-        <v>0.1206</v>
+        <v>0.6506999999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.5898</v>
+        <v>0.0721</v>
       </c>
       <c r="L14" t="n">
-        <v>0.7104</v>
+        <v>0.5786</v>
       </c>
       <c r="M14" t="n">
-        <v>-3.5536</v>
+        <v>-1.3673</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.1649</v>
+        <v>-1.8332</v>
       </c>
       <c r="O14" t="n">
-        <v>-2.3887</v>
+        <v>0.4659</v>
       </c>
       <c r="P14" t="n">
-        <v>-1.2321</v>
+        <v>1.4374</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.0534</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0.8214</v>
+        <v>1.4374</v>
       </c>
       <c r="S14" t="n">
-        <v>1.7427</v>
+        <v>0.2343</v>
       </c>
       <c r="T14" t="n">
-        <v>0.3562</v>
+        <v>0.0269</v>
       </c>
       <c r="U14" t="n">
-        <v>1.3865</v>
+        <v>0.2074</v>
       </c>
       <c r="V14" t="n">
-        <v>2.2484</v>
+        <v>-0.5893</v>
       </c>
       <c r="W14" t="n">
-        <v>2.4886</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.2402</v>
+        <v>-0.5893</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>G. RODRIGUEZ SOLER</t>
+          <t>A. BADMUS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.893</v>
+        <v>-0.925</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.2638</v>
+        <v>1.0166</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.6292</v>
+        <v>-1.9417</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.7166</v>
+        <v>-3.433</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.7611</v>
+        <v>-1.7547</v>
       </c>
       <c r="I15" t="n">
-        <v>1.0445</v>
+        <v>-1.6783</v>
       </c>
       <c r="J15" t="n">
-        <v>0.6506999999999999</v>
+        <v>0.1206</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0721</v>
+        <v>-0.5898</v>
       </c>
       <c r="L15" t="n">
-        <v>0.5786</v>
+        <v>0.7104</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.3673</v>
+        <v>-3.5536</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.8332</v>
+        <v>-1.1649</v>
       </c>
       <c r="O15" t="n">
-        <v>0.4659</v>
+        <v>-2.3887</v>
       </c>
       <c r="P15" t="n">
-        <v>1.4374</v>
+        <v>-1.2321</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-2.0534</v>
       </c>
       <c r="R15" t="n">
-        <v>1.4374</v>
+        <v>0.8214</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.0244</v>
+        <v>1.4916</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.9145</v>
+        <v>0.4608</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.11</v>
+        <v>1.0308</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.5893</v>
+        <v>2.2484</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>2.4886</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.5893</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. CARREIRA KREPS</t>
+          <t>P. LOPEZ-SANVICENTE RETA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.5533</v>
+        <v>-2.1093</v>
       </c>
       <c r="E16" t="n">
-        <v>1.4792</v>
+        <v>-1.3626</v>
       </c>
       <c r="F16" t="n">
-        <v>-3.0325</v>
+        <v>-0.7467</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.3838</v>
+        <v>-1.0944</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1106</v>
+        <v>-2.368</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.4943</v>
+        <v>1.2736</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0072</v>
+        <v>0.0284</v>
       </c>
       <c r="K16" t="n">
-        <v>0.6916</v>
+        <v>-1.3134</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.6843</v>
+        <v>1.3418</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.391</v>
+        <v>-1.1228</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.581</v>
+        <v>-1.0546</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.0682</v>
       </c>
       <c r="P16" t="n">
-        <v>0.2053</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.2053</v>
+        <v>-1.2321</v>
       </c>
       <c r="R16" t="n">
-        <v>0.4107</v>
+        <v>1.2321</v>
       </c>
       <c r="S16" t="n">
-        <v>1.9824</v>
+        <v>0.1637</v>
       </c>
       <c r="T16" t="n">
-        <v>1.6773</v>
+        <v>-0.159</v>
       </c>
       <c r="U16" t="n">
-        <v>0.305</v>
+        <v>0.3226</v>
       </c>
       <c r="V16" t="n">
-        <v>-2.3573</v>
+        <v>-1.1786</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-2.3573</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. FRITZ</t>
+          <t>G. VAZQUEZ VALLEJO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.7935</v>
+        <v>-2.2858</v>
       </c>
       <c r="E17" t="n">
-        <v>1.8852</v>
+        <v>-2.1435</v>
       </c>
       <c r="F17" t="n">
-        <v>-3.6787</v>
+        <v>-0.1423</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.2494</v>
+        <v>-2.0364</v>
       </c>
       <c r="H17" t="n">
-        <v>0.6817</v>
+        <v>-0.9992</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.9311</v>
+        <v>-1.0372</v>
       </c>
       <c r="J17" t="n">
-        <v>2.157</v>
+        <v>-1.0086</v>
       </c>
       <c r="K17" t="n">
-        <v>1.5125</v>
+        <v>0.6103</v>
       </c>
       <c r="L17" t="n">
-        <v>0.6445</v>
+        <v>-1.6188</v>
       </c>
       <c r="M17" t="n">
-        <v>-3.4064</v>
+        <v>-1.0278</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.8308</v>
+        <v>-1.6094</v>
       </c>
       <c r="O17" t="n">
-        <v>-2.5756</v>
+        <v>0.5816</v>
       </c>
       <c r="P17" t="n">
-        <v>0.4107</v>
+        <v>-0.4107</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.2321</v>
+        <v>-2.0534</v>
       </c>
       <c r="R17" t="n">
         <v>1.6427</v>
       </c>
       <c r="S17" t="n">
-        <v>1.7516</v>
+        <v>0.7506</v>
       </c>
       <c r="T17" t="n">
-        <v>1.3093</v>
+        <v>0.3292</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4422</v>
+        <v>0.4215</v>
       </c>
       <c r="V17" t="n">
-        <v>-2.7063</v>
+        <v>-0.5893</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.3491</v>
+        <v>0.5893</v>
       </c>
       <c r="X17" t="n">
-        <v>-2.3573</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>P. LOPEZ-SANVICENTE RETA</t>
+          <t>M. CARREIRA KREPS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.9611</v>
+        <v>-2.6011</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.3626</v>
+        <v>0.224</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.5985</v>
+        <v>-2.825</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.0944</v>
+        <v>-1.3838</v>
       </c>
       <c r="H18" t="n">
-        <v>-2.368</v>
+        <v>0.1106</v>
       </c>
       <c r="I18" t="n">
-        <v>1.2736</v>
+        <v>-1.4943</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0284</v>
+        <v>0.0072</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.3134</v>
+        <v>0.6916</v>
       </c>
       <c r="L18" t="n">
-        <v>1.3418</v>
+        <v>-0.6843</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.1228</v>
+        <v>-1.391</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.0546</v>
+        <v>-0.581</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.0682</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>0.2053</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.2321</v>
+        <v>-0.2053</v>
       </c>
       <c r="R18" t="n">
-        <v>1.2321</v>
+        <v>0.4107</v>
       </c>
       <c r="S18" t="n">
-        <v>0.3119</v>
+        <v>0.9346</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.159</v>
+        <v>0.4221</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4709</v>
+        <v>0.5125</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.1786</v>
+        <v>-2.3573</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.1786</v>
+        <v>-2.3573</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>O. THIAM PEDRERA</t>
+          <t>J. FRITZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.4477</v>
+        <v>-2.6531</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.121</v>
+        <v>1.153</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.3267</v>
+        <v>-3.806</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.4599</v>
+        <v>-1.2494</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.1525</v>
+        <v>0.6817</v>
       </c>
       <c r="I19" t="n">
-        <v>-2.3074</v>
+        <v>-1.9311</v>
       </c>
       <c r="J19" t="n">
-        <v>0.3863</v>
+        <v>2.157</v>
       </c>
       <c r="K19" t="n">
-        <v>0.3733</v>
+        <v>1.5125</v>
       </c>
       <c r="L19" t="n">
-        <v>0.013</v>
+        <v>0.6445</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.8462</v>
+        <v>-3.4064</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.5258</v>
+        <v>-0.8308</v>
       </c>
       <c r="O19" t="n">
-        <v>-2.3204</v>
+        <v>-2.5756</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.8481</v>
+        <v>0.4107</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.0801</v>
+        <v>-1.2321</v>
       </c>
       <c r="R19" t="n">
-        <v>1.2321</v>
+        <v>1.6427</v>
       </c>
       <c r="S19" t="n">
-        <v>1.5112</v>
+        <v>0.892</v>
       </c>
       <c r="T19" t="n">
-        <v>1.5728</v>
+        <v>0.5770999999999999</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0616</v>
+        <v>0.3149</v>
       </c>
       <c r="V19" t="n">
-        <v>0.3491</v>
+        <v>-2.7063</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>-0.3491</v>
       </c>
       <c r="X19" t="n">
-        <v>0.3491</v>
+        <v>-2.3573</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.329</v>
+        <v>-2.7607</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.2687</v>
+        <v>0.3589</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.0603</v>
+        <v>-3.1196</v>
       </c>
       <c r="G20" t="n">
         <v>-3.658</v>
@@ -2014,13 +2014,13 @@
         <v>0.4107</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.4657</v>
+        <v>0.1027</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7827</v>
+        <v>-0.1551</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3171</v>
+        <v>0.2578</v>
       </c>
       <c r="V20" t="n">
         <v>0.5893</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>G. VAZQUEZ VALLEJO</t>
+          <t>O. THIAM PEDRERA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.3823</v>
+        <v>-2.819</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.1895</v>
+        <v>-1.9578</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.1928</v>
+        <v>-0.8611</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.0364</v>
+        <v>-2.4599</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.9992</v>
+        <v>-0.1525</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.0372</v>
+        <v>-2.3074</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.0086</v>
+        <v>0.3863</v>
       </c>
       <c r="K21" t="n">
-        <v>0.6103</v>
+        <v>0.3733</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.6188</v>
+        <v>0.013</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.0278</v>
+        <v>-2.8462</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.6094</v>
+        <v>-0.5258</v>
       </c>
       <c r="O21" t="n">
-        <v>0.5816</v>
+        <v>-2.3204</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.4107</v>
+        <v>-1.8481</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.0534</v>
+        <v>-3.0801</v>
       </c>
       <c r="R21" t="n">
-        <v>1.6427</v>
+        <v>1.2321</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.346</v>
+        <v>1.14</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7169</v>
+        <v>0.736</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3709</v>
+        <v>0.404</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.5893</v>
+        <v>0.3491</v>
       </c>
       <c r="W21" t="n">
-        <v>0.5893</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.1786</v>
+        <v>0.3491</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-9.4878</v>
+        <v>-9.623799999999999</v>
       </c>
       <c r="E22" t="n">
-        <v>-7.4694</v>
+        <v>-7.7832</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.0185</v>
+        <v>-1.8406</v>
       </c>
       <c r="G22" t="n">
         <v>-4.3295</v>
@@ -2170,13 +2170,13 @@
         <v>0.616</v>
       </c>
       <c r="S22" t="n">
-        <v>0.8972</v>
+        <v>0.7613</v>
       </c>
       <c r="T22" t="n">
-        <v>0.612</v>
+        <v>0.2982</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2853</v>
+        <v>0.4631</v>
       </c>
       <c r="V22" t="n">
         <v>0.7207</v>
@@ -2203,19 +2203,19 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-23.645</v>
+        <v>-22.9479</v>
       </c>
       <c r="E23" t="n">
-        <v>-6.210599999999999</v>
+        <v>-6.2106</v>
       </c>
       <c r="F23" t="n">
-        <v>-17.4346</v>
+        <v>-16.7371</v>
       </c>
       <c r="G23" t="n">
         <v>-20.0892</v>
       </c>
       <c r="H23" t="n">
-        <v>-6.9734</v>
+        <v>-6.973399999999999</v>
       </c>
       <c r="I23" t="n">
         <v>-13.1157</v>
@@ -2224,10 +2224,10 @@
         <v>1.3461</v>
       </c>
       <c r="K23" t="n">
-        <v>0.7828000000000002</v>
+        <v>0.7827999999999997</v>
       </c>
       <c r="L23" t="n">
-        <v>0.5634999999999998</v>
+        <v>0.5634999999999997</v>
       </c>
       <c r="M23" t="n">
         <v>-21.4353</v>
@@ -2248,13 +2248,13 @@
         <v>10.2672</v>
       </c>
       <c r="S23" t="n">
-        <v>6.3148</v>
+        <v>7.0122</v>
       </c>
       <c r="T23" t="n">
-        <v>2.6715</v>
+        <v>2.6716</v>
       </c>
       <c r="U23" t="n">
-        <v>3.6432</v>
+        <v>4.3406</v>
       </c>
       <c r="V23" t="n">
         <v>-2.6838</v>
